--- a/Test Results/Excel/vulnerability_test_report.xlsx
+++ b/Test Results/Excel/vulnerability_test_report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Vulnerability Test Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Executed Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,14 +41,8 @@
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +59,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -115,9 +103,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1591,9 +1576,9 @@
           <t>test_sqli_009_update_statement_injection</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2664,9 +2649,9 @@
           <t>test_path_008_theme_file_load_path</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -3737,9 +3722,9 @@
           <t>test_crypto_007_des_3des_weak_cipher_check</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -4810,9 +4795,9 @@
           <t>test_ipc_006_binder_ipc_interface_auth</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -5883,9 +5868,9 @@
           <t>test_bio_005_biometric_auth_bypass_mock</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
@@ -6956,9 +6941,9 @@
           <t>test_nav_004_fragment_backstack_clear</t>
         </is>
       </c>
-      <c r="E175" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
@@ -8029,9 +8014,9 @@
           <t>test_reg_003_full_user_flow_security</t>
         </is>
       </c>
-      <c r="E204" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
@@ -9102,9 +9087,9 @@
           <t>test_api_002_rate_limiting_by_token</t>
         </is>
       </c>
-      <c r="E233" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
@@ -10175,9 +10160,9 @@
           <t>test_ssti_001_jinja2_template_injection</t>
         </is>
       </c>
-      <c r="E262" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E262" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
@@ -11248,9 +11233,9 @@
           <t>test_ldap_010_or_condition_ldap_inject</t>
         </is>
       </c>
-      <c r="E291" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E291" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
@@ -12321,9 +12306,9 @@
           <t>test_mass_009_created_at_timestamp_tamper</t>
         </is>
       </c>
-      <c r="E320" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E320" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F320" s="5" t="inlineStr">
@@ -13394,9 +13379,9 @@
           <t>test_dep_008_transitive_dependency_scan</t>
         </is>
       </c>
-      <c r="E349" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E349" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F349" s="5" t="inlineStr">
